--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487506_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487506_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9935</v>
+        <v>4.2564</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9329</v>
+        <v>4.0088</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0605</v>
+        <v>0.2476</v>
       </c>
       <c r="G2" t="n">
         <v>4.1051</v>
@@ -610,13 +610,13 @@
         <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0921</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5299</v>
+        <v>-0.454</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5622</v>
+        <v>-0.3751</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3905</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6729</v>
+        <v>3.8394</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0322</v>
+        <v>2.8245</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6407</v>
+        <v>1.0149</v>
       </c>
       <c r="G3" t="n">
         <v>1.7928</v>
@@ -688,13 +688,13 @@
         <v>2.3502</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8872</v>
+        <v>-0.7208</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0163</v>
+        <v>-0.2241</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8709</v>
+        <v>-0.4967</v>
       </c>
       <c r="V3" t="n">
         <v>2.3756</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5617</v>
+        <v>0.6654</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2903</v>
+        <v>-0.0263</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8521</v>
+        <v>0.6917</v>
       </c>
       <c r="G4" t="n">
         <v>0.3983</v>
@@ -766,13 +766,13 @@
         <v>0.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1534</v>
+        <v>-0.0497</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2023</v>
+        <v>0.0618</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0489</v>
+        <v>-0.1114</v>
       </c>
       <c r="V4" t="n">
         <v>1.492</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2269</v>
+        <v>0.5223</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8442</v>
+        <v>-0.6824</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0711</v>
+        <v>1.2047</v>
       </c>
       <c r="G5" t="n">
         <v>2.4874</v>
@@ -844,13 +844,13 @@
         <v>0.5875</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2432</v>
+        <v>0.0522</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1188</v>
+        <v>0.0429</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1244</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>0.3329</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0175</v>
+        <v>-0.8838</v>
       </c>
       <c r="E6" t="n">
         <v>-0.9598</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0577</v>
+        <v>0.0759</v>
       </c>
       <c r="G6" t="n">
         <v>0.3414</v>
@@ -922,13 +922,13 @@
         <v>0.1958</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5755</v>
+        <v>-0.4418</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0418</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5337</v>
+        <v>-0.4001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.0678</v>
+        <v>-2.406</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.3546</v>
+        <v>-3.8264</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2868</v>
+        <v>1.4204</v>
       </c>
       <c r="G7" t="n">
         <v>-0.656</v>
@@ -1000,13 +1000,13 @@
         <v>1.7626</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6077</v>
+        <v>-0.9459</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2298</v>
+        <v>-0.7017</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3779</v>
+        <v>-0.2442</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6083</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.732</v>
+        <v>-3.2352</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9877</v>
+        <v>-2.3573</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7443</v>
+        <v>-0.8779</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4043</v>
@@ -1078,13 +1078,13 @@
         <v>1.9585</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4647</v>
+        <v>-0.9679</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0339</v>
+        <v>-0.4035</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4308</v>
+        <v>-0.5645</v>
       </c>
       <c r="V8" t="n">
         <v>-0.8837</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>F. VIDAL PATIÑO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.9443</v>
+        <v>-4.6973</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.9867</v>
+        <v>-1.7465</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0424</v>
+        <v>-2.9507</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0744</v>
+        <v>-1.2197</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.7422</v>
+        <v>-1.4774</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.2577</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4931</v>
+        <v>-0.0104</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.3871</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.894</v>
+        <v>0.6515</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5813</v>
+        <v>-1.2093</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3551</v>
+        <v>-0.8156</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2262</v>
+        <v>-0.3938</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.6796</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q9" t="n">
-        <v>-7.834</v>
+        <v>-1.9585</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1543</v>
+        <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>3.259</v>
+        <v>-0.2817</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5731</v>
+        <v>0.2223</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6860000000000001</v>
+        <v>-0.504</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5507</v>
+        <v>-1.8249</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7673</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2166</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. VIDAL PATIÑO</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0089</v>
+        <v>-7.4857</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9512</v>
+        <v>-6.7529</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0576</v>
+        <v>-0.7328</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2197</v>
+        <v>-3.0744</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4774</v>
+        <v>-3.7422</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2577</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0104</v>
+        <v>-1.4931</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-2.3871</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6515</v>
+        <v>0.894</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2093</v>
+        <v>-1.5813</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8156</v>
+        <v>-1.3551</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3938</v>
+        <v>-0.2262</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3709</v>
+        <v>-5.6796</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9585</v>
+        <v>-7.834</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5875</v>
+        <v>2.1543</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5933</v>
+        <v>0.7177</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0176</v>
+        <v>0.8069</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.611</v>
+        <v>-0.0892</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8249</v>
+        <v>0.5507</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7673</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8249</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="11">
@@ -1267,25 +1267,25 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.3155</v>
+        <v>-9.4245</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.4094</v>
+        <v>-9.518300000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09400000000000031</v>
+        <v>0.09380000000000044</v>
       </c>
       <c r="G11" t="n">
         <v>3.7706</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.416300000000001</v>
+        <v>-4.4163</v>
       </c>
       <c r="I11" t="n">
         <v>8.1868</v>
       </c>
       <c r="J11" t="n">
-        <v>8.604199999999999</v>
+        <v>8.604200000000001</v>
       </c>
       <c r="K11" t="n">
         <v>1.3332</v>
@@ -1297,10 +1297,10 @@
         <v>-4.8337</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.7497</v>
+        <v>-5.749700000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9157</v>
+        <v>0.9157000000000002</v>
       </c>
       <c r="P11" t="n">
         <v>-10.7716</v>
@@ -1312,13 +1312,13 @@
         <v>12.73</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.3581</v>
+        <v>-3.467</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5821</v>
+        <v>-0.6912</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.776</v>
+        <v>-2.7759</v>
       </c>
       <c r="V11" t="n">
         <v>1.0438</v>
@@ -1327,7 +1327,7 @@
         <v>6.070399999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.0267</v>
+        <v>-5.026699999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.636</v>
+        <v>7.2055</v>
       </c>
       <c r="E12" t="n">
-        <v>6.6222</v>
+        <v>6.2129</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0138</v>
+        <v>0.9926</v>
       </c>
       <c r="G12" t="n">
         <v>2.4095</v>
@@ -1390,13 +1390,13 @@
         <v>3.7211</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6437</v>
+        <v>1.2132</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0545</v>
+        <v>0.6452</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5891</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.0576</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4194</v>
+        <v>3.3319</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9145</v>
+        <v>0.6075</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5049</v>
+        <v>2.7244</v>
       </c>
       <c r="G13" t="n">
         <v>-0.9418</v>
@@ -1468,13 +1468,13 @@
         <v>3.5253</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0318</v>
+        <v>0.9442</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5199</v>
+        <v>0.2129</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5119</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>M. SOUTO PARRADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0019</v>
+        <v>2.8004</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2935</v>
+        <v>1.0543</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2917</v>
+        <v>1.7461</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6056</v>
+        <v>-0.1392</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7721</v>
+        <v>-0.9882</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1665</v>
+        <v>0.8491</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4014</v>
+        <v>2.265</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6335</v>
+        <v>-0.4477</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7679</v>
+        <v>2.7126</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7958</v>
+        <v>-2.4041</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1385</v>
+        <v>-0.5406</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9344</v>
+        <v>-1.8635</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3917</v>
+        <v>1.7626</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9585</v>
+        <v>-2.1543</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5668</v>
+        <v>3.917</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0058</v>
+        <v>0.9591</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2423</v>
+        <v>0.4505</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2365</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2178</v>
+        <v>0.2178</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6083</v>
+        <v>0.4931</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8961</v>
+        <v>2.1679</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.5146</v>
+        <v>2.2935</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4107</v>
+        <v>-0.1257</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.5621</v>
+        <v>2.6056</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4549</v>
+        <v>2.7721</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.017</v>
+        <v>-0.1665</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5622</v>
+        <v>3.4014</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9955</v>
+        <v>2.6335</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.5576</v>
+        <v>0.7679</v>
       </c>
       <c r="M15" t="n">
-        <v>-2</v>
+        <v>-0.7958</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5406</v>
+        <v>0.1385</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4594</v>
+        <v>-0.9344</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.1128</v>
+        <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>4.1128</v>
+        <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4594</v>
+        <v>0.1717</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9438</v>
+        <v>0.2423</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5156</v>
+        <v>-0.0706</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9988</v>
+        <v>-0.2178</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2166</v>
+        <v>0.6083</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2178</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SOUTO PARRADO</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2589</v>
+        <v>0.5769</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1332</v>
+        <v>-2.4356</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1257</v>
+        <v>3.0125</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1392</v>
+        <v>-2.5621</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9882</v>
+        <v>1.4549</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8491</v>
+        <v>-4.017</v>
       </c>
       <c r="J16" t="n">
-        <v>2.265</v>
+        <v>-0.5622</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4477</v>
+        <v>1.9955</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7126</v>
+        <v>-2.5576</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4041</v>
+        <v>-2</v>
       </c>
       <c r="N16" t="n">
         <v>-0.5406</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8635</v>
+        <v>-1.4594</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7626</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1543</v>
+        <v>-4.1128</v>
       </c>
       <c r="R16" t="n">
-        <v>3.917</v>
+        <v>4.1128</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5823</v>
+        <v>2.1402</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4705</v>
+        <v>1.0228</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1118</v>
+        <v>1.1175</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2178</v>
+        <v>0.9988</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4931</v>
+        <v>1.2166</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2754</v>
+        <v>-0.2178</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3622</v>
+        <v>0.2553</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3622</v>
+        <v>0.2553</v>
       </c>
       <c r="G17" t="n">
         <v>0.1364</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2257</v>
+        <v>0.1188</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2257</v>
+        <v>0.1188</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1543</v>
+        <v>0.181</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1543</v>
+        <v>0.181</v>
       </c>
       <c r="G18" t="n">
         <v>0.1364</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.635</v>
+        <v>-0.6083</v>
       </c>
       <c r="E19" t="n">
         <v>-0.7602</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1252</v>
+        <v>0.1519</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0445</v>
@@ -1936,13 +1936,13 @@
         <v>0.5875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.178</v>
+        <v>-0.1513</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0592</v>
+        <v>-0.0325</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8704</v>
+        <v>-0.6464</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2503</v>
+        <v>-2.3526</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3799</v>
+        <v>1.7062</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7384</v>
@@ -2014,13 +2014,13 @@
         <v>3.1336</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3968</v>
+        <v>0.6208</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6099</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2131</v>
+        <v>0.1132</v>
       </c>
       <c r="V20" t="n">
         <v>0.2754</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4248</v>
+        <v>-0.723</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.0451</v>
+        <v>-3.1241</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6203</v>
+        <v>2.4011</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9299</v>
@@ -2092,13 +2092,13 @@
         <v>1.7626</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7275</v>
+        <v>-0.0257</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2298</v>
+        <v>-0.3088</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4977</v>
+        <v>0.283</v>
       </c>
       <c r="V21" t="n">
         <v>0.6659</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4832</v>
+        <v>-2.1789</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4872</v>
+        <v>-1.5895</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.996</v>
+        <v>-0.5894</v>
       </c>
       <c r="G22" t="n">
         <v>0.2975</v>
@@ -2170,13 +2170,13 @@
         <v>1.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>0.065</v>
+        <v>0.3692</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2247</v>
+        <v>0.1223</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1597</v>
+        <v>0.2469</v>
       </c>
       <c r="V22" t="n">
         <v>-3.0415</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10.3154</v>
+        <v>12.3623</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.09399999999999986</v>
+        <v>-0.09379999999999922</v>
       </c>
       <c r="F23" t="n">
-        <v>10.4093</v>
+        <v>12.456</v>
       </c>
       <c r="G23" t="n">
         <v>-3.7705</v>
       </c>
       <c r="H23" t="n">
-        <v>4.4163</v>
+        <v>4.416300000000001</v>
       </c>
       <c r="I23" t="n">
         <v>-8.1869</v>
@@ -2224,10 +2224,10 @@
         <v>4.833699999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>5.749599999999999</v>
+        <v>5.749600000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.9157999999999997</v>
+        <v>-0.9157999999999993</v>
       </c>
       <c r="M23" t="n">
         <v>-8.604399999999998</v>
@@ -2248,22 +2248,22 @@
         <v>23.5018</v>
       </c>
       <c r="S23" t="n">
-        <v>4.3582</v>
+        <v>6.404800000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>2.776000000000001</v>
+        <v>2.776</v>
       </c>
       <c r="U23" t="n">
-        <v>1.582100000000001</v>
+        <v>3.6289</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0438</v>
       </c>
       <c r="W23" t="n">
-        <v>5.0266</v>
+        <v>5.026599999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.070499999999999</v>
+        <v>-6.0705</v>
       </c>
     </row>
   </sheetData>
